--- a/tame_output/ON/bt/strategyON_20240820.xlsx
+++ b/tame_output/ON/bt/strategyON_20240820.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>47.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.5%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.3%</t>
+          <t>-48.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-665.7%</t>
+          <t>-657.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-159.2%</t>
+          <t>-155.9%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-328.6%</t>
+          <t>-329.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -48948,16 +48948,16 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.866907019738585</v>
+        <v>3.75533600426874</v>
       </c>
       <c r="C2061" t="n">
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.040840447640442</v>
+        <v>-4.958576886641072</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.170433326857613</v>
+        <v>2.203338751257361</v>
       </c>
       <c r="F2061" t="n">
         <v>0.7344069391165065</v>

--- a/tame_output/ON/bt/strategyON_20240820.xlsx
+++ b/tame_output/ON/bt/strategyON_20240820.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>53.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.0%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-657.4%</t>
+          <t>-660.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.9%</t>
+          <t>-157.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-329.3%</t>
+          <t>-330.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-150.6%</t>
+          <t>-143.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>20.9%</t>
         </is>
       </c>
     </row>
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.11175488237729</v>
+        <v>-3.042433389145875</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.218309617198494</v>
+        <v>2.24603821449106</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.067485831259087</v>
+        <v>1.136807324490503</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.10385949321861</v>
+        <v>4.145452389157459</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.273323307904545</v>
+        <v>-3.20400181467313</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.152116257197744</v>
+        <v>2.179844854490311</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9407029074612078</v>
+        <v>1.010024400692623</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.026223749150034</v>
+        <v>4.067816645088884</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.75459613538935</v>
+        <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.405624600002098</v>
+        <v>-3.336303106770683</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.112269147224642</v>
+        <v>2.139997744517208</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9407029074612078</v>
+        <v>1.010024400692623</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.039297156015953</v>
+        <v>4.080890051954802</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.591492910841328</v>
+        <v>-3.522171417609913</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.02992701967189</v>
+        <v>2.057655616964456</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7821373141412601</v>
+        <v>0.8514588073726754</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.936162996806924</v>
+        <v>3.977755892745774</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.619393697950801</v>
+        <v>-3.550072204719386</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.017290745955103</v>
+        <v>2.045019343247668</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7475403899983253</v>
+        <v>0.8168618832297406</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.913928883448166</v>
+        <v>3.955521779387015</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.741919800653695</v>
+        <v>-3.67259830742228</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.965044748851144</v>
+        <v>1.99277334614371</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6250142872954314</v>
+        <v>0.6943357805268467</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.837177665803628</v>
+        <v>3.878770561742477</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.972434296839284</v>
+        <v>-3.903112803607868</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.939544909967412</v>
+        <v>1.967273507259979</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3944997911098427</v>
+        <v>0.463821284341258</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.765574927682779</v>
+        <v>3.807167823621628</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.229155114834107</v>
+        <v>-4.159833621602692</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.97716830177133</v>
+        <v>2.004896899063896</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3554067101974432</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.840837902198337</v>
+        <v>3.882430798137186</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.383141532610248</v>
+        <v>-4.313820039378832</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.984554003806513</v>
+        <v>2.01228260109908</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3554067101974432</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.909818171343977</v>
+        <v>3.951411067282826</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.332619628782582</v>
+        <v>-4.263298135551167</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.990813967457701</v>
+        <v>2.018542564750267</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3554067101974432</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.895869373464098</v>
+        <v>3.937462269402947</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.585094782790306</v>
+        <v>-4.515773289558891</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.901694394910025</v>
+        <v>1.929422992202591</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3554067101974432</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.907739862519512</v>
+        <v>3.949332758458361</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.877990539269718</v>
+        <v>-4.808669046038303</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.785746626837204</v>
+        <v>1.81347522412977</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3554067101974432</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.908950397038455</v>
+        <v>3.950543292977304</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.064654667404526</v>
+        <v>-4.995333174173111</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.715202717810602</v>
+        <v>1.742931315103168</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.259346246141468</v>
+        <v>0.3286677393728833</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.897028756771041</v>
+        <v>3.93862165270989</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.210675354318488</v>
+        <v>-5.141353861087073</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.651872295781207</v>
+        <v>1.679600893073772</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.250263154347611</v>
+        <v>0.3195846475790263</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.886656754430916</v>
+        <v>3.928249650369765</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.302389363428073</v>
+        <v>-5.233067870196658</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.777390748836417</v>
+        <v>1.805119346128983</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.250263154347611</v>
+        <v>0.3195846475790263</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.04886081112996</v>
+        <v>4.090453707068809</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.334041022488043</v>
+        <v>-5.264719529256627</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.759576723176243</v>
+        <v>1.787305320468809</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2450946971031708</v>
+        <v>0.3144161903345861</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.04060637474711</v>
+        <v>4.082199270685959</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.415975840756926</v>
+        <v>-5.346654347525511</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.737032213437181</v>
+        <v>1.764760810729747</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2351599515160906</v>
+        <v>0.3044814447475059</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.044874944963353</v>
+        <v>4.086467840902202</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.517951963005333</v>
+        <v>-5.448630469773918</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.70516740299372</v>
+        <v>1.732896000286286</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.133183829267683</v>
+        <v>0.2025053224990984</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.992614910070211</v>
+        <v>4.034207806009061</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231808</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.407945679528112</v>
+        <v>-5.338624186296697</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.741322803628784</v>
+        <v>1.76905140092135</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1563884011849582</v>
+        <v>0.2257098944163736</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.998690540464752</v>
+        <v>4.040283436403601</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.264886103787186</v>
+        <v>-5.19556461055577</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.802796644647129</v>
+        <v>1.830525241939695</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1644018277749375</v>
+        <v>0.2337233210063528</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.007748607140713</v>
+        <v>4.049341503079563</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.963439378315348</v>
+        <v>-4.894117885083933</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.9306362177184</v>
+        <v>1.958364815010966</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.5351700464781901</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.195877525306352</v>
+        <v>4.237470421245201</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.988029622550532</v>
+        <v>-4.918708129319117</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.921771297777037</v>
+        <v>1.949499895069603</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.5351700464781901</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.196848703059063</v>
+        <v>4.238441598997912</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.936991246544012</v>
+        <v>-4.867669753312597</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.9430295525594</v>
+        <v>1.970758149851966</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.5351700464781901</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.197691607438817</v>
+        <v>4.239284503377666</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.895851951677381</v>
+        <v>-4.826530458445966</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.978523369380198</v>
+        <v>2.006251966672764</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5069878481134056</v>
+        <v>0.5763093413448209</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.241413283232942</v>
+        <v>4.283006179171791</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.799217039658741</v>
+        <v>-4.729895546427326</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.833361330311589</v>
+        <v>1.861089927604155</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6036227601320455</v>
+        <v>0.6729442533634609</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.11557822656806</v>
+        <v>4.157171122506909</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.929797774189583</v>
+        <v>-4.860476280958168</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.784631080573216</v>
+        <v>1.812359677865782</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.473042025601203</v>
+        <v>0.5423635188326184</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.040731829923518</v>
+        <v>4.082324725862367</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.765301439998622</v>
+        <v>-4.695979946767206</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.834856433325683</v>
+        <v>1.862585030618249</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6375383597921649</v>
+        <v>0.7068598530235802</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.123856449514178</v>
+        <v>4.165449345453027</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.792671372683054</v>
+        <v>-4.723349879451638</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.82309617068834</v>
+        <v>1.850824767980906</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6375383597921649</v>
+        <v>0.7068598530235802</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.123044159950608</v>
+        <v>4.164637055889457</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.803056567572943</v>
+        <v>-4.733735074341528</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.828810871857456</v>
+        <v>1.856539469150022</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6271531649022756</v>
+        <v>0.6964746581336909</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.126681822141746</v>
+        <v>4.168274718080595</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.821644726295168</v>
+        <v>-4.752323233063753</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.892212614144992</v>
+        <v>1.919941211437558</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6085650061800503</v>
+        <v>0.6778864994114655</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.186365932684836</v>
+        <v>4.227958828623685</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.821943272991204</v>
+        <v>-4.752621779759789</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.888962206284876</v>
+        <v>1.916690803577442</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6082664594840144</v>
+        <v>0.6775879527154296</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.183055815485513</v>
+        <v>4.224648711424362</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.721120139300776</v>
+        <v>-4.651798646069361</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.933822354700438</v>
+        <v>1.961550951993004</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6207306749683682</v>
+        <v>0.6900521681997834</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.195065239715517</v>
+        <v>4.236658135654366</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.530338778548369</v>
+        <v>-4.461017285316954</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.010264152479944</v>
+        <v>2.03799274977251</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8115120357207756</v>
+        <v>0.8808335289521908</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.309663309645504</v>
+        <v>4.351256205584354</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.511821924506549</v>
+        <v>-4.442500431275134</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.997507739834269</v>
+        <v>2.025236337126835</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8244421651459838</v>
+        <v>0.893763658377399</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.297258233038226</v>
+        <v>4.338851128977075</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.486628740005231</v>
+        <v>-4.417307246773816</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.042551950246855</v>
+        <v>2.07028054753942</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8496353496473021</v>
+        <v>0.9189568428787174</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.347341080351075</v>
+        <v>4.388933976289925</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.474574613092268</v>
+        <v>-4.405253119860853</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.041060168913477</v>
+        <v>2.068788766206043</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.861689476560265</v>
+        <v>0.9310109697916802</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.348260124400291</v>
+        <v>4.389853020339141</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.481197859782626</v>
+        <v>-4.411876366551211</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.04029150042147</v>
+        <v>2.068020097714036</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8550662298699065</v>
+        <v>0.9243877231013218</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.346166806570212</v>
+        <v>4.387759702509061</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.378317270254033</v>
+        <v>-4.308995777022618</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.094294762110789</v>
+        <v>2.122023359403356</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9579468193984995</v>
+        <v>1.027268312629915</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.42074618616525</v>
+        <v>4.4623390821041</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.40175930943412</v>
+        <v>-4.332437816202705</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.105120616612349</v>
+        <v>2.132849213904915</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9579468193984995</v>
+        <v>1.027268312629915</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.440948856338844</v>
+        <v>4.482541752277694</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781706</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.419831817725732</v>
+        <v>-4.350510324494317</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.097891613295705</v>
+        <v>2.12562021058827</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9579468193984995</v>
+        <v>1.027268312629915</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.440948856338844</v>
+        <v>4.482541752277694</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082835</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.651005611602364</v>
+        <v>-4.581684118370949</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.965674009338518</v>
+        <v>1.993402606631084</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9579468193984995</v>
+        <v>1.027268312629915</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.401200769932311</v>
+        <v>4.44279366587116</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943587</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.619719591061909</v>
+        <v>-4.550398097830493</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.98521103655164</v>
+        <v>2.012939633844206</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9892328399389547</v>
+        <v>1.05855433317037</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.426995001253524</v>
+        <v>4.468587897192373</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677825</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.466694198948624</v>
+        <v>-4.397372705717209</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.145592192969858</v>
+        <v>2.173320790262424</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.142258232052239</v>
+        <v>1.211579725283654</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.617981236094399</v>
+        <v>4.659574132033248</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073885</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.495001512821895</v>
+        <v>-4.425680019590479</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.321735492328842</v>
+        <v>2.349464089621408</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.142258232052239</v>
+        <v>1.211579725283654</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.805447461002691</v>
+        <v>4.84704035694154</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.69913580090317</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.661594737935417</v>
+        <v>-4.592273244704002</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.224501153637516</v>
+        <v>2.252229750930082</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9756650069387163</v>
+        <v>1.044986500170132</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.67489447728866</v>
+        <v>4.716487373227509</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.708202704568384</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.488530358553117</v>
+        <v>-4.419208865321702</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.297403308052154</v>
+        <v>2.32513190534472</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9756650069387163</v>
+        <v>1.044986500170132</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.678570879950378</v>
+        <v>4.720163775889227</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.740601586682206</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.45928437809742</v>
+        <v>-4.389962884866005</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.306719755357928</v>
+        <v>2.334448352650494</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9756650069387163</v>
+        <v>1.044986500170132</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.676188935073872</v>
+        <v>4.717781831012722</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539107</v>
+        <v>3.699424827539109</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.566209925975271</v>
+        <v>-4.496888432743856</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.261242775364422</v>
+        <v>2.288971372656988</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8687394590608649</v>
+        <v>0.9380609522922801</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.609326845504797</v>
+        <v>4.650919741443646</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983737</v>
+        <v>3.689962785983739</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.71122848448252</v>
+        <v>-4.641906991251105</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.204664154104757</v>
+        <v>2.232392751397323</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7237209005536164</v>
+        <v>0.7930423937850316</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.523744512543682</v>
+        <v>4.565337408482531</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.71187261496975</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.829570250267238</v>
+        <v>-4.760248757035822</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.257258687048623</v>
+        <v>2.284987284341189</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7344069391165065</v>
+        <v>0.8037284323479217</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.630087374939169</v>
+        <v>4.671680270878018</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.71489923707354</v>
       </c>
       <c r="C2059" t="n">
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.880980672587945</v>
+        <v>-4.81165917935653</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.234480215246278</v>
+        <v>2.262208812538844</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7344069391165065</v>
+        <v>0.8037284323479217</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.627873072065108</v>
+        <v>4.669465968003957</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720065</v>
+        <v>3.704778134720067</v>
       </c>
       <c r="C2060" t="n">
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.960400123795697</v>
+        <v>-4.891078630564282</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.202615562837467</v>
+        <v>2.230344160130033</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7344069391165065</v>
+        <v>0.8037284323479217</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.627776200139397</v>
+        <v>4.669369096078246</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.75533600426874</v>
+        <v>3.817810413434367</v>
       </c>
       <c r="C2061" t="n">
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.958576886641072</v>
+        <v>-4.9865416284815</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.203338751257361</v>
+        <v>2.19215285452119</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7344069391165065</v>
+        <v>0.8037284323479217</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.627770093697441</v>
+        <v>4.66936298963629</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240820.xlsx
+++ b/tame_output/ON/bt/strategyON_20240820.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>121.1%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>-14.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2061"/>
+  <dimension ref="A1:G2062"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389349</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833456</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912983</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539893</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811007</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382918</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.817810413434367</v>
+        <v>3.736825137581134</v>
       </c>
       <c r="C2061" t="n">
         <v>4.187125930227537</v>
@@ -48964,6 +48964,29 @@
       </c>
       <c r="G2061" t="n">
         <v>4.66936298963629</v>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" s="2" t="n">
+        <v>45524</v>
+      </c>
+      <c r="B2062" t="n">
+        <v>3.81529566811775</v>
+      </c>
+      <c r="C2062" t="n">
+        <v>4.326869030454121</v>
+      </c>
+      <c r="D2062" t="n">
+        <v>-4.9865416284815</v>
+      </c>
+      <c r="E2062" t="n">
+        <v>2.19215285452119</v>
+      </c>
+      <c r="F2062" t="n">
+        <v>0.8037284323479217</v>
+      </c>
+      <c r="G2062" t="n">
+        <v>4.319932827440489</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240820.xlsx
+++ b/tame_output/ON/bt/strategyON_20240820.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>55.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>81.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-78.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-42.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.4%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.6%</t>
+          <t>430.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-660.2%</t>
+          <t>-670.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.0%</t>
+          <t>-161.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-330.3%</t>
+          <t>-329.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-143.6%</t>
+          <t>-145.4%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.20400181467313</v>
+        <v>-3.181240133976942</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.179844854490311</v>
+        <v>2.188949526768786</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.010024400692623</v>
+        <v>0.9936729270837679</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.067816645088884</v>
+        <v>4.058005760923571</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.336303106770683</v>
+        <v>-3.313541426074496</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.139997744517208</v>
+        <v>2.149102416795683</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.010024400692623</v>
+        <v>0.9936729270837679</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.080890051954802</v>
+        <v>4.071079167789489</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378393</v>
+        <v>3.749882691378394</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.522171417609913</v>
+        <v>-3.499409736913726</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.057655616964456</v>
+        <v>2.066760289242931</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8514588073726754</v>
+        <v>0.8351073337638202</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.977755892745774</v>
+        <v>3.967945008580461</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006976</v>
+        <v>3.715819895006977</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.550072204719386</v>
+        <v>-3.527310524023199</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.045019343247668</v>
+        <v>2.054124015526144</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8168618832297406</v>
+        <v>0.8005104096208854</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.955521779387015</v>
+        <v>3.945710895221702</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.67259830742228</v>
+        <v>-3.649836626726092</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.99277334614371</v>
+        <v>2.001878018422185</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6943357805268467</v>
+        <v>0.6779843069179915</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.878770561742477</v>
+        <v>3.868959677577164</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585939</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.903112803607868</v>
+        <v>-3.880351122911681</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.967273507259979</v>
+        <v>1.976378179538453</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.463821284341258</v>
+        <v>0.4474698107324028</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.807167823621628</v>
+        <v>3.797356939456315</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.159833621602692</v>
+        <v>-4.137071940906505</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.004896899063896</v>
+        <v>2.01400157134237</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3554067101974432</v>
+        <v>0.3390552365885879</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.882430798137186</v>
+        <v>3.872619913971873</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.313820039378832</v>
+        <v>-4.291058358682646</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.01228260109908</v>
+        <v>2.021387273377554</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3554067101974432</v>
+        <v>0.3390552365885879</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.951411067282826</v>
+        <v>3.941600183117512</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.263298135551167</v>
+        <v>-4.24053645485498</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.018542564750267</v>
+        <v>2.027647237028742</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3554067101974432</v>
+        <v>0.3390552365885879</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.937462269402947</v>
+        <v>3.927651385237634</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.515773289558891</v>
+        <v>-4.493011608862704</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.929422992202591</v>
+        <v>1.938527664481065</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3554067101974432</v>
+        <v>0.3390552365885879</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.949332758458361</v>
+        <v>3.939521874293048</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.808669046038303</v>
+        <v>-4.785907365342116</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.81347522412977</v>
+        <v>1.822579896408244</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3554067101974432</v>
+        <v>0.3390552365885879</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.950543292977304</v>
+        <v>3.940732408811991</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251947</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.995333174173111</v>
+        <v>-4.972571493476925</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.742931315103168</v>
+        <v>1.752035987381643</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3286677393728833</v>
+        <v>0.312316265764028</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.93862165270989</v>
+        <v>3.928810768544577</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916203</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.141353861087073</v>
+        <v>-5.118592180390887</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.679600893073772</v>
+        <v>1.688705565352247</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3195846475790263</v>
+        <v>0.3032331739701711</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.928249650369765</v>
+        <v>3.918438766204452</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830329</v>
+        <v>3.66796230683033</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.233067870196658</v>
+        <v>-5.210306189500471</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.805119346128983</v>
+        <v>1.814224018407458</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3195846475790263</v>
+        <v>0.3032331739701711</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.090453707068809</v>
+        <v>4.080642822903497</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.264719529256627</v>
+        <v>-5.241957848560441</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.787305320468809</v>
+        <v>1.796409992747284</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3144161903345861</v>
+        <v>0.2980647167257309</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.082199270685959</v>
+        <v>4.072388386520646</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.346654347525511</v>
+        <v>-5.323892666829324</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.764760810729747</v>
+        <v>1.773865483008222</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3044814447475059</v>
+        <v>0.2881299711386507</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.086467840902202</v>
+        <v>4.07665695673689</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.448630469773918</v>
+        <v>-5.425868789077732</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.732896000286286</v>
+        <v>1.742000672564761</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2025053224990984</v>
+        <v>0.1861538488902431</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.034207806009061</v>
+        <v>4.024396921843747</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.338624186296697</v>
+        <v>-5.429320174765517</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.76905140092135</v>
+        <v>1.732773005533822</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2257098944163736</v>
+        <v>0.2083710796915001</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.040283436403601</v>
+        <v>4.029880147568677</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.785563924818524</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.19556461055577</v>
+        <v>-5.286260599024592</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.830525241939695</v>
+        <v>1.794246846552166</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2337233210063528</v>
+        <v>0.2163845062814794</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.049341503079563</v>
+        <v>4.038938214244639</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.77723741205179</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.894117885083933</v>
+        <v>-4.984813873552755</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.958364815010966</v>
+        <v>1.922086419623438</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5351700464781901</v>
+        <v>0.5178312317533167</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.237470421245201</v>
+        <v>4.227067132410277</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679626</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.918708129319117</v>
+        <v>-5.009404117787938</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.949499895069603</v>
+        <v>1.913221499682074</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5351700464781901</v>
+        <v>0.5178312317533167</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.238441598997912</v>
+        <v>4.228038310162987</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.867669753312597</v>
+        <v>-4.958365741781418</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.970758149851966</v>
+        <v>1.934479754464438</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5351700464781901</v>
+        <v>0.5178312317533167</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.239284503377666</v>
+        <v>4.228881214542743</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.826530458445966</v>
+        <v>-4.917226446914787</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.006251966672764</v>
+        <v>1.969973571285236</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5763093413448209</v>
+        <v>0.5589705266199475</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.283006179171791</v>
+        <v>4.272602890336866</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.82575293270048</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.729895546427326</v>
+        <v>-4.820591534896147</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.861089927604155</v>
+        <v>1.824811532216626</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6729442533634609</v>
+        <v>0.6556054386385874</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.157171122506909</v>
+        <v>4.146767833671985</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.860476280958168</v>
+        <v>-4.95117226942699</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.812359677865782</v>
+        <v>1.776081282478253</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5423635188326184</v>
+        <v>0.5250247041077449</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.082324725862367</v>
+        <v>4.071921437027443</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833456</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.695979946767206</v>
+        <v>-4.786675935236028</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.862585030618249</v>
+        <v>1.82630663523072</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.7068598530235802</v>
+        <v>0.6895210382987068</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.165449345453027</v>
+        <v>4.155046056618103</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077629</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.723349879451638</v>
+        <v>-4.77780275082211</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.850824767980906</v>
+        <v>1.829043619432717</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.7068598530235802</v>
+        <v>0.6895210382987068</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.164637055889457</v>
+        <v>4.154233767054532</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.733735074341528</v>
+        <v>-4.788187945711999</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.856539469150022</v>
+        <v>1.834758320601834</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6964746581336909</v>
+        <v>0.6791358434088175</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.168274718080595</v>
+        <v>4.157871429245672</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.752323233063753</v>
+        <v>-4.806776104434224</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.919941211437558</v>
+        <v>1.898160062889369</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6778864994114655</v>
+        <v>0.6605476846865921</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.227958828623685</v>
+        <v>4.217555539788761</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.752621779759789</v>
+        <v>-4.80707465113026</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.916690803577442</v>
+        <v>1.894909655029253</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6775879527154296</v>
+        <v>0.6602491379905562</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.224648711424362</v>
+        <v>4.214245422589438</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.651798646069361</v>
+        <v>-4.706251517439832</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.961550951993004</v>
+        <v>1.939769803444816</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6900521681997834</v>
+        <v>0.67271335347491</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.236658135654366</v>
+        <v>4.226254846819442</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.461017285316954</v>
+        <v>-4.515470156687424</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.03799274977251</v>
+        <v>2.016211601224322</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8808335289521908</v>
+        <v>0.8634947142273174</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.351256205584354</v>
+        <v>4.34085291674943</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.77523303390608</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.442500431275134</v>
+        <v>-4.496953302645604</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.025236337126835</v>
+        <v>2.003455188578647</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.893763658377399</v>
+        <v>0.8764248436525256</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.338851128977075</v>
+        <v>4.328447840142151</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912983</v>
+        <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.417307246773816</v>
+        <v>-4.471760118144286</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.07028054753942</v>
+        <v>2.048499398991233</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9189568428787174</v>
+        <v>0.901618028153844</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.388933976289925</v>
+        <v>4.378530687455001</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539893</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.405253119860853</v>
+        <v>-4.459705991231323</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.068788766206043</v>
+        <v>2.047007617657855</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9310109697916802</v>
+        <v>0.9136721550668068</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.389853020339141</v>
+        <v>4.379449731504216</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811007</v>
+        <v>3.725010844811009</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.411876366551211</v>
+        <v>-4.466329237921681</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.068020097714036</v>
+        <v>2.046238949165848</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9243877231013218</v>
+        <v>0.9070489083764484</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.387759702509061</v>
+        <v>4.377356413674137</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382918</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.308995777022618</v>
+        <v>-4.363448648393089</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.122023359403356</v>
+        <v>2.100242210855168</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.027268312629915</v>
+        <v>1.009929497905041</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.4623390821041</v>
+        <v>4.451935793269175</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760317</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.332437816202705</v>
+        <v>-4.386890687573175</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.132849213904915</v>
+        <v>2.111068065356727</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.027268312629915</v>
+        <v>1.009929497905041</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.482541752277694</v>
+        <v>4.47213846344277</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781706</v>
+        <v>3.666767386781708</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.350510324494317</v>
+        <v>-4.404963195864787</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.12562021058827</v>
+        <v>2.103839062040082</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.027268312629915</v>
+        <v>1.009929497905041</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.482541752277694</v>
+        <v>4.47213846344277</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082835</v>
+        <v>3.670068888082837</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.581684118370949</v>
+        <v>-4.636136989741419</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.993402606631084</v>
+        <v>1.971621458082896</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.027268312629915</v>
+        <v>1.009929497905041</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.44279366587116</v>
+        <v>4.432390377036236</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943587</v>
+        <v>3.745593333943589</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.550398097830493</v>
+        <v>-4.604850969200964</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.012939633844206</v>
+        <v>1.991158485296018</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.05855433317037</v>
+        <v>1.041215518445497</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.468587897192373</v>
+        <v>4.458184608357449</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677825</v>
+        <v>3.730590658677827</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.397372705717209</v>
+        <v>-4.451825577087679</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.173320790262424</v>
+        <v>2.151539641714236</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.211579725283654</v>
+        <v>1.194240910558781</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.659574132033248</v>
+        <v>4.649170843198323</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073885</v>
+        <v>3.741298518073886</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.425680019590479</v>
+        <v>-4.48013289096095</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.349464089621408</v>
+        <v>2.32768294107322</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.211579725283654</v>
+        <v>1.194240910558781</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.84704035694154</v>
+        <v>4.836637068106616</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69913580090317</v>
+        <v>3.699135800903171</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.592273244704002</v>
+        <v>-4.646726116074472</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.252229750930082</v>
+        <v>2.230448602381894</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.044986500170132</v>
+        <v>1.027647685445258</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.716487373227509</v>
+        <v>4.706084084392585</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568384</v>
+        <v>3.708202704568386</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.419208865321702</v>
+        <v>-4.473661736692172</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.32513190534472</v>
+        <v>2.303350756796531</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.044986500170132</v>
+        <v>1.027647685445258</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.720163775889227</v>
+        <v>4.709760487054303</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682206</v>
+        <v>3.740601586682208</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.389962884866005</v>
+        <v>-4.444415756236475</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.334448352650494</v>
+        <v>2.312667204102305</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.044986500170132</v>
+        <v>1.027647685445258</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.717781831012722</v>
+        <v>4.707378542177798</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539109</v>
+        <v>3.699424827539111</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.496888432743856</v>
+        <v>-4.551341304114326</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.288971372656988</v>
+        <v>2.2671902241088</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9380609522922801</v>
+        <v>0.9207221375674067</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.650919741443646</v>
+        <v>4.640516452608722</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983739</v>
+        <v>3.689962785983741</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.641906991251105</v>
+        <v>-4.696359862621575</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.232392751397323</v>
+        <v>2.210611602849135</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7930423937850316</v>
+        <v>0.7757035790601582</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.565337408482531</v>
+        <v>4.554934119647608</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71187261496975</v>
+        <v>3.711872614969752</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.760248757035822</v>
+        <v>-4.814701628406293</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.284987284341189</v>
+        <v>2.263206135793001</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.8037284323479217</v>
+        <v>0.7863896176230483</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.671680270878018</v>
+        <v>4.661276982043094</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.71489923707354</v>
+        <v>3.714899237073542</v>
       </c>
       <c r="C2059" t="n">
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.81165917935653</v>
+        <v>-4.866112050727001</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.262208812538844</v>
+        <v>2.240427663990656</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.8037284323479217</v>
+        <v>0.7863896176230483</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.669465968003957</v>
+        <v>4.659062679169033</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720067</v>
+        <v>3.704778134720069</v>
       </c>
       <c r="C2060" t="n">
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.891078630564282</v>
+        <v>-4.945531501934752</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.230344160130033</v>
+        <v>2.208563011581845</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.8037284323479217</v>
+        <v>0.7863896176230483</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.669369096078246</v>
+        <v>4.658965807243322</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581134</v>
+        <v>3.736825137581135</v>
       </c>
       <c r="C2061" t="n">
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.9865416284815</v>
+        <v>-5.086507710586898</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.19215285452119</v>
+        <v>2.15216642167903</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.8037284323479217</v>
+        <v>0.7863896176230483</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.66936298963629</v>
+        <v>4.658959700801366</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.81529566811775</v>
+        <v>3.835619265315273</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.326869030454121</v>
+        <v>4.327279521974964</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.9865416284815</v>
+        <v>-5.086507710586898</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.19215285452119</v>
+        <v>2.15216642167903</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.8037284323479217</v>
+        <v>0.7863896176230483</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.319932827440489</v>
+        <v>4.320343318961331</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240820.xlsx
+++ b/tame_output/ON/bt/strategyON_20240820.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.2%</t>
+          <t>107.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-42.7%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.5%</t>
+          <t>430.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-670.2%</t>
+          <t>-661.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-161.0%</t>
+          <t>-157.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-329.9%</t>
+          <t>-328.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-145.4%</t>
+          <t>-150.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.042433389145875</v>
+        <v>-3.11175488237729</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.24603821449106</v>
+        <v>2.218309617198494</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.136807324490503</v>
+        <v>1.067485831259087</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.145452389157459</v>
+        <v>4.10385949321861</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.181240133976942</v>
+        <v>-3.273323307904545</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.188949526768786</v>
+        <v>2.152116257197744</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9936729270837679</v>
+        <v>0.9407029074612078</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.058005760923571</v>
+        <v>4.026223749150034</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.313541426074496</v>
+        <v>-3.405624600002098</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.149102416795683</v>
+        <v>2.112269147224642</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9936729270837679</v>
+        <v>0.9407029074612078</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.071079167789489</v>
+        <v>4.039297156015953</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.499409736913726</v>
+        <v>-3.591492910841328</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.066760289242931</v>
+        <v>2.02992701967189</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8351073337638202</v>
+        <v>0.7821373141412601</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.967945008580461</v>
+        <v>3.936162996806924</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.527310524023199</v>
+        <v>-3.619393697950801</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.054124015526144</v>
+        <v>2.017290745955103</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8005104096208854</v>
+        <v>0.7475403899983253</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.945710895221702</v>
+        <v>3.913928883448166</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.649836626726092</v>
+        <v>-3.741919800653695</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.001878018422185</v>
+        <v>1.965044748851144</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6779843069179915</v>
+        <v>0.6250142872954314</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.868959677577164</v>
+        <v>3.837177665803628</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.880351122911681</v>
+        <v>-3.972434296839284</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.976378179538453</v>
+        <v>1.939544909967412</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4474698107324028</v>
+        <v>0.3944997911098427</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.797356939456315</v>
+        <v>3.765574927682779</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.137071940906505</v>
+        <v>-4.229155114834107</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.01400157134237</v>
+        <v>1.97716830177133</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3390552365885879</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.872619913971873</v>
+        <v>3.840837902198337</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.291058358682646</v>
+        <v>-4.383141532610248</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.021387273377554</v>
+        <v>1.984554003806513</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3390552365885879</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.941600183117512</v>
+        <v>3.909818171343977</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.24053645485498</v>
+        <v>-4.332619628782582</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.027647237028742</v>
+        <v>1.990813967457701</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3390552365885879</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.927651385237634</v>
+        <v>3.895869373464098</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.493011608862704</v>
+        <v>-4.585094782790306</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.938527664481065</v>
+        <v>1.901694394910025</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3390552365885879</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.939521874293048</v>
+        <v>3.907739862519512</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.785907365342116</v>
+        <v>-4.877990539269718</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.822579896408244</v>
+        <v>1.785746626837204</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3390552365885879</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.940732408811991</v>
+        <v>3.908950397038455</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.972571493476925</v>
+        <v>-5.064654667404526</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.752035987381643</v>
+        <v>1.715202717810602</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.312316265764028</v>
+        <v>0.259346246141468</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.928810768544577</v>
+        <v>3.897028756771041</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.118592180390887</v>
+        <v>-5.210675354318488</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.688705565352247</v>
+        <v>1.651872295781207</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3032331739701711</v>
+        <v>0.250263154347611</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.918438766204452</v>
+        <v>3.886656754430916</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.210306189500471</v>
+        <v>-5.302389363428073</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.814224018407458</v>
+        <v>1.777390748836417</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3032331739701711</v>
+        <v>0.250263154347611</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.080642822903497</v>
+        <v>4.04886081112996</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.241957848560441</v>
+        <v>-5.334041022488043</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.796409992747284</v>
+        <v>1.759576723176243</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2980647167257309</v>
+        <v>0.2450946971031708</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.072388386520646</v>
+        <v>4.04060637474711</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.323892666829324</v>
+        <v>-5.415975840756926</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.773865483008222</v>
+        <v>1.737032213437181</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2881299711386507</v>
+        <v>0.2351599515160906</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.07665695673689</v>
+        <v>4.044874944963353</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.425868789077732</v>
+        <v>-5.517951963005333</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.742000672564761</v>
+        <v>1.70516740299372</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1861538488902431</v>
+        <v>0.133183829267683</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.024396921843747</v>
+        <v>3.992614910070211</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.429320174765517</v>
+        <v>-5.407945679528112</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.732773005533822</v>
+        <v>1.741322803628784</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2083710796915001</v>
+        <v>0.1563884011849582</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.029880147568677</v>
+        <v>3.998690540464752</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.286260599024592</v>
+        <v>-5.264886103787186</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.794246846552166</v>
+        <v>1.802796644647129</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2163845062814794</v>
+        <v>0.1644018277749375</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.038938214244639</v>
+        <v>4.007748607140713</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.984813873552755</v>
+        <v>-4.963439378315348</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.922086419623438</v>
+        <v>1.9306362177184</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5178312317533167</v>
+        <v>0.4658485532467748</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.227067132410277</v>
+        <v>4.195877525306352</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.009404117787938</v>
+        <v>-4.988029622550532</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.913221499682074</v>
+        <v>1.921771297777037</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5178312317533167</v>
+        <v>0.4658485532467748</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.228038310162987</v>
+        <v>4.196848703059063</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.958365741781418</v>
+        <v>-4.936991246544012</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.934479754464438</v>
+        <v>1.9430295525594</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5178312317533167</v>
+        <v>0.4658485532467748</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.228881214542743</v>
+        <v>4.197691607438817</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.917226446914787</v>
+        <v>-4.895851951677381</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.969973571285236</v>
+        <v>1.978523369380198</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5589705266199475</v>
+        <v>0.5069878481134056</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.272602890336866</v>
+        <v>4.241413283232942</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.820591534896147</v>
+        <v>-4.799217039658741</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.824811532216626</v>
+        <v>1.833361330311589</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6556054386385874</v>
+        <v>0.6036227601320455</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.146767833671985</v>
+        <v>4.11557822656806</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.95117226942699</v>
+        <v>-4.929797774189583</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.776081282478253</v>
+        <v>1.784631080573216</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5250247041077449</v>
+        <v>0.473042025601203</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.071921437027443</v>
+        <v>4.040731829923518</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.786675935236028</v>
+        <v>-4.765301439998622</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.82630663523072</v>
+        <v>1.834856433325683</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6895210382987068</v>
+        <v>0.6375383597921649</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.155046056618103</v>
+        <v>4.123856449514178</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.77780275082211</v>
+        <v>-4.732486552627668</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.829043619432717</v>
+        <v>1.847170098710494</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6895210382987068</v>
+        <v>0.6375383597921649</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.154233767054532</v>
+        <v>4.123044159950608</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.788187945711999</v>
+        <v>-4.742871747517557</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.834758320601834</v>
+        <v>1.852884799879611</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6791358434088175</v>
+        <v>0.6271531649022756</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.157871429245672</v>
+        <v>4.126681822141746</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.806776104434224</v>
+        <v>-4.761459906239782</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.898160062889369</v>
+        <v>1.916286542167146</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6605476846865921</v>
+        <v>0.6085650061800503</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.217555539788761</v>
+        <v>4.186365932684836</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.80707465113026</v>
+        <v>-4.761758452935818</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.894909655029253</v>
+        <v>1.91303613430703</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6602491379905562</v>
+        <v>0.6082664594840144</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.214245422589438</v>
+        <v>4.183055815485513</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.706251517439832</v>
+        <v>-4.66093531924539</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.939769803444816</v>
+        <v>1.957896282722592</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.67271335347491</v>
+        <v>0.6207306749683682</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.226254846819442</v>
+        <v>4.195065239715517</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.515470156687424</v>
+        <v>-4.470153958492983</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.016211601224322</v>
+        <v>2.034338080502099</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8634947142273174</v>
+        <v>0.8115120357207756</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.34085291674943</v>
+        <v>4.309663309645504</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.496953302645604</v>
+        <v>-4.451637104451162</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.003455188578647</v>
+        <v>2.021581667856424</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8764248436525256</v>
+        <v>0.8244421651459838</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.328447840142151</v>
+        <v>4.297258233038226</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.471760118144286</v>
+        <v>-4.426443919949844</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.048499398991233</v>
+        <v>2.066625878269009</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.901618028153844</v>
+        <v>0.8496353496473021</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.378530687455001</v>
+        <v>4.347341080351075</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.459705991231323</v>
+        <v>-4.414389793036881</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.047007617657855</v>
+        <v>2.065134096935632</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9136721550668068</v>
+        <v>0.861689476560265</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.379449731504216</v>
+        <v>4.348260124400291</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.466329237921681</v>
+        <v>-4.42101303972724</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.046238949165848</v>
+        <v>2.064365428443625</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9070489083764484</v>
+        <v>0.8550662298699065</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.377356413674137</v>
+        <v>4.346166806570212</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.363448648393089</v>
+        <v>-4.318132450198647</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.100242210855168</v>
+        <v>2.118368690132944</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.009929497905041</v>
+        <v>0.9579468193984995</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.451935793269175</v>
+        <v>4.42074618616525</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.386890687573175</v>
+        <v>-4.341574489378734</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.111068065356727</v>
+        <v>2.129194544634504</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.009929497905041</v>
+        <v>0.9579468193984995</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.47213846344277</v>
+        <v>4.440948856338844</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.404963195864787</v>
+        <v>-4.359646997670345</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.103839062040082</v>
+        <v>2.121965541317859</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.009929497905041</v>
+        <v>0.9579468193984995</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.47213846344277</v>
+        <v>4.440948856338844</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.636136989741419</v>
+        <v>-4.590820791546977</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.971621458082896</v>
+        <v>1.989747937360673</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.009929497905041</v>
+        <v>0.9579468193984995</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.432390377036236</v>
+        <v>4.401200769932311</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.604850969200964</v>
+        <v>-4.559534771006522</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.991158485296018</v>
+        <v>2.009284964573795</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.041215518445497</v>
+        <v>0.9892328399389547</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.458184608357449</v>
+        <v>4.426995001253524</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.451825577087679</v>
+        <v>-4.406509378893237</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.151539641714236</v>
+        <v>2.169666120992013</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.194240910558781</v>
+        <v>1.142258232052239</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.649170843198323</v>
+        <v>4.617981236094399</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.48013289096095</v>
+        <v>-4.434816692766508</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.32768294107322</v>
+        <v>2.345809420350997</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.194240910558781</v>
+        <v>1.142258232052239</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.836637068106616</v>
+        <v>4.805447461002691</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.646726116074472</v>
+        <v>-4.60140991788003</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.230448602381894</v>
+        <v>2.248575081659671</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.027647685445258</v>
+        <v>0.9756650069387163</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.706084084392585</v>
+        <v>4.67489447728866</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.473661736692172</v>
+        <v>-4.42834553849773</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.303350756796531</v>
+        <v>2.321477236074308</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.027647685445258</v>
+        <v>0.9756650069387163</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.709760487054303</v>
+        <v>4.678570879950378</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.444415756236475</v>
+        <v>-4.399099558042034</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.312667204102305</v>
+        <v>2.330793683380082</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.027647685445258</v>
+        <v>0.9756650069387163</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.707378542177798</v>
+        <v>4.676188935073872</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.551341304114326</v>
+        <v>-4.506025105919885</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.2671902241088</v>
+        <v>2.285316703386576</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9207221375674067</v>
+        <v>0.8687394590608649</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.640516452608722</v>
+        <v>4.609326845504797</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.696359862621575</v>
+        <v>-4.651043664427133</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.210611602849135</v>
+        <v>2.228738082126911</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7757035790601582</v>
+        <v>0.7237209005536164</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.554934119647608</v>
+        <v>4.523744512543682</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.814701628406293</v>
+        <v>-4.769385430211851</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.263206135793001</v>
+        <v>2.281332615070777</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7863896176230483</v>
+        <v>0.7344069391165065</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.661276982043094</v>
+        <v>4.630087374939169</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.866112050727001</v>
+        <v>-4.820795852532559</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.240427663990656</v>
+        <v>2.258554143268433</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7863896176230483</v>
+        <v>0.7344069391165065</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.659062679169033</v>
+        <v>4.627873072065108</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.945531501934752</v>
+        <v>-4.90021530374031</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.208563011581845</v>
+        <v>2.226689490859622</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7863896176230483</v>
+        <v>0.7344069391165065</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.658965807243322</v>
+        <v>4.627776200139397</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.086507710586898</v>
+        <v>-4.995678301657528</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.15216642167903</v>
+        <v>2.188498185250778</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7863896176230483</v>
+        <v>0.7344069391165065</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.658959700801366</v>
+        <v>4.627770093697441</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,13 +48977,13 @@
         <v>4.327279521974964</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.086507710586898</v>
+        <v>-4.995678301657528</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.15216642167903</v>
+        <v>2.188498185250778</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7863896176230483</v>
+        <v>0.7344069391165065</v>
       </c>
       <c r="G2062" t="n">
         <v>4.320343318961331</v>

--- a/tame_output/ON/bt/strategyON_20240820.xlsx
+++ b/tame_output/ON/bt/strategyON_20240820.xlsx
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>121.1%</t>
+          <t>106.9%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-78.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-44.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-661.1%</t>
+          <t>-668.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.4%</t>
+          <t>-160.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-328.8%</t>
+          <t>-329.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-150.6%</t>
+          <t>-157.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>12.4%</t>
         </is>
       </c>
     </row>
@@ -48974,19 +48974,19 @@
         <v>3.835619265315273</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.327279521974964</v>
+        <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.995678301657528</v>
+        <v>-5.064578603947173</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.188498185250778</v>
+        <v>2.159034460897531</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7344069391165065</v>
+        <v>0.6655066368268616</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.320343318961331</v>
+        <v>4.584526308886264</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240820.xlsx
+++ b/tame_output/ON/bt/strategyON_20240820.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-44.2%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-48.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-668.0%</t>
+          <t>-658.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.3%</t>
+          <t>-156.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-329.5%</t>
+          <t>-328.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-157.4%</t>
+          <t>-141.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>22.0%</t>
         </is>
       </c>
     </row>
@@ -48379,10 +48379,10 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.732486552627668</v>
+        <v>-4.792671372683054</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.847170098710494</v>
+        <v>1.82309617068834</v>
       </c>
       <c r="F2036" t="n">
         <v>0.6375383597921649</v>
@@ -48402,10 +48402,10 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.742871747517557</v>
+        <v>-4.803056567572943</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.852884799879611</v>
+        <v>1.828810871857456</v>
       </c>
       <c r="F2037" t="n">
         <v>0.6271531649022756</v>
@@ -48425,10 +48425,10 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.761459906239782</v>
+        <v>-4.821644726295168</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.916286542167146</v>
+        <v>1.892212614144992</v>
       </c>
       <c r="F2038" t="n">
         <v>0.6085650061800503</v>
@@ -48448,10 +48448,10 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.761758452935818</v>
+        <v>-4.821943272991204</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.91303613430703</v>
+        <v>1.888962206284876</v>
       </c>
       <c r="F2039" t="n">
         <v>0.6082664594840144</v>
@@ -48471,10 +48471,10 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.66093531924539</v>
+        <v>-4.721120139300776</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.957896282722592</v>
+        <v>1.933822354700438</v>
       </c>
       <c r="F2040" t="n">
         <v>0.6207306749683682</v>
@@ -48494,10 +48494,10 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.470153958492983</v>
+        <v>-4.530338778548369</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.034338080502099</v>
+        <v>2.010264152479944</v>
       </c>
       <c r="F2041" t="n">
         <v>0.8115120357207756</v>
@@ -48517,10 +48517,10 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.451637104451162</v>
+        <v>-4.511821924506549</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.021581667856424</v>
+        <v>1.997507739834269</v>
       </c>
       <c r="F2042" t="n">
         <v>0.8244421651459838</v>
@@ -48540,10 +48540,10 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.426443919949844</v>
+        <v>-4.486628740005231</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.066625878269009</v>
+        <v>2.042551950246855</v>
       </c>
       <c r="F2043" t="n">
         <v>0.8496353496473021</v>
@@ -48563,10 +48563,10 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.414389793036881</v>
+        <v>-4.474574613092268</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.065134096935632</v>
+        <v>2.041060168913477</v>
       </c>
       <c r="F2044" t="n">
         <v>0.861689476560265</v>
@@ -48586,10 +48586,10 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.42101303972724</v>
+        <v>-4.481197859782626</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.064365428443625</v>
+        <v>2.04029150042147</v>
       </c>
       <c r="F2045" t="n">
         <v>0.8550662298699065</v>
@@ -48609,10 +48609,10 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.318132450198647</v>
+        <v>-4.378317270254033</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.118368690132944</v>
+        <v>2.094294762110789</v>
       </c>
       <c r="F2046" t="n">
         <v>0.9579468193984995</v>
@@ -48632,10 +48632,10 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.341574489378734</v>
+        <v>-4.40175930943412</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.129194544634504</v>
+        <v>2.105120616612349</v>
       </c>
       <c r="F2047" t="n">
         <v>0.9579468193984995</v>
@@ -48655,10 +48655,10 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.359646997670345</v>
+        <v>-4.419831817725732</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.121965541317859</v>
+        <v>2.097891613295705</v>
       </c>
       <c r="F2048" t="n">
         <v>0.9579468193984995</v>
@@ -48678,10 +48678,10 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.590820791546977</v>
+        <v>-4.651005611602364</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.989747937360673</v>
+        <v>1.965674009338518</v>
       </c>
       <c r="F2049" t="n">
         <v>0.9579468193984995</v>
@@ -48701,10 +48701,10 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.559534771006522</v>
+        <v>-4.619719591061909</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.009284964573795</v>
+        <v>1.98521103655164</v>
       </c>
       <c r="F2050" t="n">
         <v>0.9892328399389547</v>
@@ -48724,10 +48724,10 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.406509378893237</v>
+        <v>-4.466694198948624</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.169666120992013</v>
+        <v>2.145592192969858</v>
       </c>
       <c r="F2051" t="n">
         <v>1.142258232052239</v>
@@ -48747,10 +48747,10 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.434816692766508</v>
+        <v>-4.495001512821895</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.345809420350997</v>
+        <v>2.321735492328842</v>
       </c>
       <c r="F2052" t="n">
         <v>1.142258232052239</v>
@@ -48770,10 +48770,10 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.60140991788003</v>
+        <v>-4.661594737935417</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.248575081659671</v>
+        <v>2.224501153637516</v>
       </c>
       <c r="F2053" t="n">
         <v>0.9756650069387163</v>
@@ -48793,10 +48793,10 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.42834553849773</v>
+        <v>-4.488530358553117</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.321477236074308</v>
+        <v>2.297403308052154</v>
       </c>
       <c r="F2054" t="n">
         <v>0.9756650069387163</v>
@@ -48816,10 +48816,10 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.399099558042034</v>
+        <v>-4.45928437809742</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.330793683380082</v>
+        <v>2.306719755357928</v>
       </c>
       <c r="F2055" t="n">
         <v>0.9756650069387163</v>
@@ -48839,10 +48839,10 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.506025105919885</v>
+        <v>-4.566209925975271</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.285316703386576</v>
+        <v>2.261242775364422</v>
       </c>
       <c r="F2056" t="n">
         <v>0.8687394590608649</v>
@@ -48862,10 +48862,10 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.651043664427133</v>
+        <v>-4.71122848448252</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.228738082126911</v>
+        <v>2.204664154104757</v>
       </c>
       <c r="F2057" t="n">
         <v>0.7237209005536164</v>
@@ -48885,10 +48885,10 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.769385430211851</v>
+        <v>-4.829570250267238</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.281332615070777</v>
+        <v>2.257258687048623</v>
       </c>
       <c r="F2058" t="n">
         <v>0.7344069391165065</v>
@@ -48908,10 +48908,10 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.820795852532559</v>
+        <v>-4.880980672587945</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.258554143268433</v>
+        <v>2.234480215246278</v>
       </c>
       <c r="F2059" t="n">
         <v>0.7344069391165065</v>
@@ -48931,10 +48931,10 @@
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.90021530374031</v>
+        <v>-4.960400123795697</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.226689490859622</v>
+        <v>2.202615562837467</v>
       </c>
       <c r="F2060" t="n">
         <v>0.7344069391165065</v>
@@ -48948,16 +48948,16 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581135</v>
+        <v>3.736825137581136</v>
       </c>
       <c r="C2061" t="n">
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.995678301657528</v>
+        <v>-5.055863121712915</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.188498185250778</v>
+        <v>2.164424257228624</v>
       </c>
       <c r="F2061" t="n">
         <v>0.7344069391165065</v>
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.835619265315273</v>
+        <v>3.742887409280906</v>
       </c>
       <c r="C2062" t="n">
         <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.064578603947173</v>
+        <v>-4.964838890932984</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.159034460897531</v>
+        <v>2.198930346103206</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6655066368268616</v>
+        <v>0.8254311698964374</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.584526308886264</v>
+        <v>4.680481028728011</v>
       </c>
     </row>
   </sheetData>
